--- a/resources/templates/standard/D1100-03.xlsx
+++ b/resources/templates/standard/D1100-03.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>제품 안전교육 보고서</t>
   </si>
@@ -516,12 +519,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -542,20 +547,20 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4"/>
       <c r="AE1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
@@ -632,7 +637,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -650,7 +655,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -671,7 +676,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -708,7 +713,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -745,7 +750,7 @@
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -782,7 +787,7 @@
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -959,7 +964,7 @@
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1451,7 +1456,7 @@
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -1628,7 +1633,7 @@
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
